--- a/diseases/d002/2015-2019.xlsx
+++ b/diseases/d002/2015-2019.xlsx
@@ -1584,9 +1584,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1732,9 +1729,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -3164,9 +3158,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3312,9 +3303,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4744,9 +4732,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4892,9 +4877,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6324,9 +6306,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6472,9 +6451,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8200,9 +8176,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8348,9 +8321,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9780,9 +9750,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9928,9 +9895,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11360,9 +11324,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11508,9 +11469,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13088,9 +13046,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13236,9 +13191,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -14816,9 +14768,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14964,9 +14913,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16544,9 +16490,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16692,9 +16635,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18420,9 +18360,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18568,9 +18505,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20000,9 +19934,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -20148,9 +20079,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22103,9 +22031,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -22251,9 +22176,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23831,9 +23753,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23979,9 +23898,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -25411,9 +25327,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -25559,9 +25472,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -27139,9 +27049,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -27287,9 +27194,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -28719,9 +28623,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -28867,9 +28768,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -30299,9 +30197,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -30447,9 +30342,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32027,9 +31919,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -32175,9 +32064,6 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.01909861051878893</v>
       </c>
@@ -33755,9 +33641,6 @@
       <c r="O211" t="n">
         <v>3</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -33903,9 +33786,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -35483,9 +35363,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -35631,9 +35508,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -37359,9 +37233,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -37507,9 +37378,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -39087,9 +38955,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -39235,9 +39100,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -40667,9 +40529,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -40815,9 +40674,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -42770,9 +42626,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -43954,9 +43807,6 @@
       <c r="O276" t="n">
         <v>2</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -45138,9 +44988,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -46470,9 +46317,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -47654,9 +47498,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -48838,9 +48679,6 @@
       <c r="O309" t="n">
         <v>1</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -50170,9 +50008,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -51354,9 +51189,6 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -52686,9 +52518,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -54018,9 +53847,6 @@
       <c r="O344" t="n">
         <v>1</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -55350,9 +55176,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -56682,9 +56505,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -58241,9 +58061,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -59425,9 +59242,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -60609,9 +60423,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -61941,9 +61752,6 @@
       <c r="O397" t="n">
         <v>0</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0</v>
       </c>
@@ -63125,9 +62933,6 @@
       <c r="O405" t="n">
         <v>0</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0</v>
       </c>
@@ -64457,9 +64262,6 @@
       <c r="O414" t="n">
         <v>0</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0</v>
       </c>
@@ -65641,9 +65443,6 @@
       <c r="O422" t="n">
         <v>2</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.00387289964422382</v>
       </c>
@@ -66973,9 +66772,6 @@
       <c r="O431" t="n">
         <v>0</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0</v>
       </c>
@@ -68453,9 +68249,6 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
@@ -69933,9 +69726,6 @@
       <c r="O451" t="n">
         <v>0</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0</v>
       </c>
@@ -71117,9 +70907,6 @@
       <c r="O459" t="n">
         <v>0</v>
       </c>
-      <c r="Q459" t="n">
-        <v>0</v>
-      </c>
       <c r="R459" t="n">
         <v>0</v>
       </c>
@@ -72449,9 +72236,6 @@
       <c r="O468" t="n">
         <v>0</v>
       </c>
-      <c r="Q468" t="n">
-        <v>0</v>
-      </c>
       <c r="R468" t="n">
         <v>0</v>
       </c>
@@ -74008,9 +73792,6 @@
       <c r="O478" t="n">
         <v>0</v>
       </c>
-      <c r="Q478" t="n">
-        <v>0</v>
-      </c>
       <c r="R478" t="n">
         <v>0</v>
       </c>
@@ -75340,9 +75121,6 @@
       <c r="O487" t="n">
         <v>0</v>
       </c>
-      <c r="Q487" t="n">
-        <v>0</v>
-      </c>
       <c r="R487" t="n">
         <v>0</v>
       </c>
@@ -76524,9 +76302,6 @@
       <c r="O495" t="n">
         <v>0</v>
       </c>
-      <c r="Q495" t="n">
-        <v>0</v>
-      </c>
       <c r="R495" t="n">
         <v>0</v>
       </c>
@@ -77708,9 +77483,6 @@
       <c r="O503" t="n">
         <v>0</v>
       </c>
-      <c r="Q503" t="n">
-        <v>0</v>
-      </c>
       <c r="R503" t="n">
         <v>0</v>
       </c>
@@ -78892,9 +78664,6 @@
       <c r="O511" t="n">
         <v>0</v>
       </c>
-      <c r="Q511" t="n">
-        <v>0</v>
-      </c>
       <c r="R511" t="n">
         <v>0</v>
       </c>
@@ -80224,9 +79993,6 @@
       <c r="O520" t="n">
         <v>0</v>
       </c>
-      <c r="Q520" t="n">
-        <v>0</v>
-      </c>
       <c r="R520" t="n">
         <v>0</v>
       </c>
@@ -81408,9 +81174,6 @@
       <c r="O528" t="n">
         <v>0</v>
       </c>
-      <c r="Q528" t="n">
-        <v>0</v>
-      </c>
       <c r="R528" t="n">
         <v>0</v>
       </c>
@@ -82592,9 +82355,6 @@
       <c r="O536" t="n">
         <v>0</v>
       </c>
-      <c r="Q536" t="n">
-        <v>0</v>
-      </c>
       <c r="R536" t="n">
         <v>0</v>
       </c>
@@ -83924,9 +83684,6 @@
       <c r="O545" t="n">
         <v>0</v>
       </c>
-      <c r="Q545" t="n">
-        <v>0</v>
-      </c>
       <c r="R545" t="n">
         <v>0</v>
       </c>
@@ -85108,9 +84865,6 @@
       <c r="O553" t="n">
         <v>1</v>
       </c>
-      <c r="Q553" t="n">
-        <v>0</v>
-      </c>
       <c r="R553" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -86440,9 +86194,6 @@
       <c r="O562" t="n">
         <v>0</v>
       </c>
-      <c r="Q562" t="n">
-        <v>0</v>
-      </c>
       <c r="R562" t="n">
         <v>0</v>
       </c>
@@ -87622,9 +87373,6 @@
         <v>0</v>
       </c>
       <c r="O570" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q570" t="n">
         <v>0</v>
       </c>
       <c r="R570" t="n">
